--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1020,6 +1020,53 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">120006</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">PermanentUpgrade_120006_Name</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">PermanentUpgrade_120006_Desc</t>
+        </is>
+      </c>
+      <c r="E7" s="0">
+        <v>3</v>
+      </c>
+      <c r="F7" s="0">
+        <v>5</v>
+      </c>
+      <c r="G7" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Passive</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">HealthRegen</t>
+        </is>
+      </c>
+      <c r="J7" s="0">
+        <v>2</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1067,6 +1067,53 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">120007</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">PermanentUpgrade_120007_Name</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">PermanentUpgrade_120007_Desc</t>
+        </is>
+      </c>
+      <c r="E8" s="0">
+        <v>5</v>
+      </c>
+      <c r="F8" s="0">
+        <v>2</v>
+      </c>
+      <c r="G8" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Passive</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">FreeReroll</t>
+        </is>
+      </c>
+      <c r="J8" s="0">
+        <v>1</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="J7" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="0">
         <v>0</v>

--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -832,53 +832,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120002</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120002_Name</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120002_Desc</t>
-        </is>
-      </c>
-      <c r="E3" s="0">
-        <v>3</v>
-      </c>
-      <c r="F3" s="0">
-        <v>5</v>
-      </c>
-      <c r="G3" s="0">
-        <v>1.3</v>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteRewardRate</t>
-        </is>
-      </c>
-      <c r="J3" s="0">
-        <v>100</v>
-      </c>
-      <c r="L3" s="0">
-        <v>0</v>
-      </c>
-    </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <v/>

--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="E2" s="0">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F2" s="0">
         <v>3</v>
       </c>
       <c r="G2" s="0">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H2" s="0" t="inlineStr">
         <v/>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E4" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F4" s="0">
         <v>10</v>
       </c>
       <c r="G4" s="0">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <v/>
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="E5" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F5" s="0">
         <v>10</v>
       </c>
       <c r="G5" s="0">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <v/>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="E6" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6" s="0">
         <v>10</v>
       </c>
       <c r="G6" s="0">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <v/>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="E7" s="0">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F7" s="0">
         <v>5</v>
       </c>
       <c r="G7" s="0">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <v/>
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="E8" s="0">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="F8" s="0">
         <v>2</v>
       </c>
       <c r="G8" s="0">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <v/>

--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -13,198 +13,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">Body_KMD_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoldGainRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxTurretCount</t>
+  </si>
   <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">Monster_10003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10016_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster_10005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
+    <t xml:space="preserve">stat_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpGainRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealthRegen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FreeReroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_value_per_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
   </si>
 </sst>
 </file>
@@ -709,147 +643,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M8"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <v>name</v>
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <v>need_money</v>
-        <is>
-          <t xml:space="preserve">need_money</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <v>max_upgrade_count</v>
-        <is>
-          <t xml:space="preserve">max_upgrade_count</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <v>growth_rate</v>
-        <is>
-          <t xml:space="preserve">growth_rate</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <v>category</v>
-        <is>
-          <t xml:space="preserve">category</t>
-        </is>
-      </c>
-      <c r="I1" s="0" t="inlineStr">
-        <v>passive_type</v>
-        <is>
-          <t xml:space="preserve">passive_type</t>
-        </is>
-      </c>
-      <c r="J1" s="0" t="inlineStr">
-        <v>passive_value_per_level</v>
-        <is>
-          <t xml:space="preserve">passive_value_per_level</t>
-        </is>
-      </c>
-      <c r="K1" s="0" t="inlineStr">
-        <v>stat_type</v>
-        <is>
-          <t xml:space="preserve">stat_type</t>
-        </is>
-      </c>
-      <c r="L1" s="0" t="inlineStr">
-        <v>stat_value</v>
-        <is>
-          <t xml:space="preserve">stat_value</t>
-        </is>
+    <row r="1" spans="1:12">
+      <c r="A1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120001</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120001_Name</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120001_Desc</t>
-        </is>
+    <row r="2" spans="1:12">
+      <c r="A2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>31</v>
       </c>
       <c r="E2" s="0">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F2" s="0">
+        <v>10</v>
+      </c>
+      <c r="G2" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="0">
-        <v>5</v>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MaxTurretCount</t>
-        </is>
-      </c>
       <c r="J2" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L2" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120003</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120003_Name</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120003_Desc</t>
-        </is>
+    <row r="3" spans="1:12">
+      <c r="A3" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="0">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0">
+        <v>10</v>
+      </c>
+      <c r="G3" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="0">
+        <v>10</v>
+      </c>
+      <c r="L3" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>1</v>
       </c>
       <c r="E4" s="0">
         <v>10</v>
@@ -860,17 +774,11 @@
       <c r="G4" s="0">
         <v>1.5</v>
       </c>
-      <c r="H4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MaxHp</t>
-        </is>
+      <c r="H4" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>41</v>
       </c>
       <c r="J4" s="0">
         <v>10</v>
@@ -879,139 +787,103 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120004</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120004_Name</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120004_Desc</t>
-        </is>
+    <row r="5" spans="1:12">
+      <c r="A5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="0">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F5" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">GoldGainRate</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>13</v>
       </c>
       <c r="J5" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L5" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120005</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120005_Name</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120005_Desc</t>
-        </is>
+    <row r="6" spans="1:12">
+      <c r="A6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F6" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G6" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExpGainRate</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="J6" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L6" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120006</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120006_Name</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120006_Desc</t>
-        </is>
+    <row r="7" spans="1:12">
+      <c r="A7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>18</v>
       </c>
       <c r="E7" s="0">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F7" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="0">
-        <v>2</v>
-      </c>
-      <c r="H7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">HealthRegen</t>
-        </is>
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>14</v>
       </c>
       <c r="J7" s="0">
         <v>1</v>
@@ -1020,53 +892,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">120007</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120007_Name</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">PermanentUpgrade_120007_Desc</t>
-        </is>
-      </c>
-      <c r="E8" s="0">
-        <v>150</v>
-      </c>
-      <c r="F8" s="0">
-        <v>2</v>
-      </c>
-      <c r="G8" s="0">
-        <v>3.5</v>
-      </c>
-      <c r="H8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Passive</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FreeReroll</t>
-        </is>
-      </c>
-      <c r="J8" s="0">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
+  <pageMargins left="0.748055577278137" right="0.748055577278137" top="0.984305560588837" bottom="0.984305560588837" header="0.511805534362793" footer="0.511805534362793"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -13,132 +13,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_value_per_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PermanentUpgrade_120004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repair</t>
+  </si>
   <si>
     <t xml:space="preserve">Body_KMD_05</t>
   </si>
   <si>
-    <t xml:space="preserve">Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoldGainRate</t>
+    <t xml:space="preserve">Reroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealthRegen</t>
   </si>
   <si>
     <t xml:space="preserve">MaxTurretCount</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">growth_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExpGainRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HealthRegen</t>
-  </si>
-  <si>
     <t xml:space="preserve">FreeReroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_value_per_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PermanentUpgrade_120005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
   </si>
 </sst>
 </file>
@@ -644,59 +617,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="0" t="s">
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="0" t="s">
+      <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>11</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="0" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>25</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>31</v>
       </c>
       <c r="E2" s="0">
         <v>10</v>
@@ -708,10 +681,10 @@
         <v>1.5</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="J2" s="0">
         <v>10</v>
@@ -722,31 +695,34 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="0" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>26</v>
       </c>
       <c r="E3" s="0">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F3" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G3" s="0">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J3" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -754,34 +730,34 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="0" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="E4" s="0">
+        <v>100</v>
+      </c>
+      <c r="F4" s="0">
+        <v>3</v>
+      </c>
+      <c r="G4" s="0">
+        <v>5</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="0">
         <v>1</v>
-      </c>
-      <c r="E4" s="0">
-        <v>10</v>
-      </c>
-      <c r="F4" s="0">
-        <v>10</v>
-      </c>
-      <c r="G4" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="0">
-        <v>10</v>
       </c>
       <c r="L4" s="0">
         <v>0</v>
@@ -789,106 +765,36 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="0" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E5" s="0">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F5" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="0">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="J5" s="0">
         <v>1</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0">
-        <v>100</v>
-      </c>
-      <c r="F6" s="0">
-        <v>3</v>
-      </c>
-      <c r="G6" s="0">
-        <v>5</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" s="0">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="0">
-        <v>150</v>
-      </c>
-      <c r="F7" s="0">
-        <v>2</v>
-      </c>
-      <c r="G7" s="0">
-        <v>3.5</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="0">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0">
         <v>0</v>
       </c>
     </row>

--- a/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/PermanentUpgradeData.xlsx
@@ -672,13 +672,13 @@
         <v>25</v>
       </c>
       <c r="E2" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" s="0">
         <v>10</v>
       </c>
       <c r="G2" s="0">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>12</v>
@@ -707,13 +707,13 @@
         <v>26</v>
       </c>
       <c r="E3" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F3" s="0">
         <v>5</v>
       </c>
       <c r="G3" s="0">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>12</v>
@@ -742,13 +742,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="0">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F4" s="0">
         <v>3</v>
       </c>
       <c r="G4" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>12</v>
@@ -777,13 +777,13 @@
         <v>28</v>
       </c>
       <c r="E5" s="0">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="F5" s="0">
         <v>2</v>
       </c>
       <c r="G5" s="0">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>12</v>
